--- a/output/pdf_financials_xlsx/HARD.xlsx
+++ b/output/pdf_financials_xlsx/HARD.xlsx
@@ -615,7 +615,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.028577</v>
       </c>
     </row>
     <row r="13">
@@ -873,7 +873,7 @@
         <v>0.147818</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.437733</v>
+        <v>-0.46631</v>
       </c>
     </row>
     <row r="28">
@@ -905,7 +905,7 @@
         <v>0.147818</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.437733</v>
+        <v>-0.46631</v>
       </c>
     </row>
     <row r="30">
@@ -982,13 +982,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.006258</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.130995</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.000977</v>
       </c>
     </row>
     <row r="35">
@@ -1014,13 +1014,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.006258</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.130995</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.000977</v>
       </c>
     </row>
     <row r="37">
@@ -1206,13 +1206,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.006258</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.130995</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.000977</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">

--- a/output/pdf_financials_xlsx/HARD.xlsx
+++ b/output/pdf_financials_xlsx/HARD.xlsx
@@ -3574,7 +3574,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
